--- a/MAJSushiConfig/ig/StructureDefinition-fr-medication-request-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-medication-request-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -481,7 +481,7 @@
     <t>notCovered</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-not-covered-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-not-covered-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -741,7 +741,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
+Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-document|0.1.0)</t>
   </si>
   <si>
     <t>Produit de santé</t>
@@ -783,7 +783,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
 </t>
   </si>
   <si>
@@ -816,7 +816,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-encounter-care-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-encounter-care-document|0.1.0)
 </t>
   </si>
   <si>
@@ -891,7 +891,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitioner-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitioner-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1008,7 +1008,7 @@
     <t>MedicationRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
+    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1058,7 +1058,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-medication-request-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-care-plan-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-service-request-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-immunization-recommendation-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-medication-request-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-care-plan-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-immunization-recommendation-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1825,7 +1825,7 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-edqm-document|0.1.0</t>
   </si>
   <si>
     <t>Dosage.route</t>
